--- a/docs/competition/引用体检-老师试用记录表.xlsx
+++ b/docs/competition/引用体检-老师试用记录表.xlsx
@@ -1326,7 +1326,7 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>复制修正版清单，或下载核查报告</t>
+          <t>复制修正版清单或规范参考文献，或下载核查报告</t>
         </is>
       </c>
       <c r="C74" s="10" t="n"/>

--- a/docs/competition/引用体检-老师试用记录表.xlsx
+++ b/docs/competition/引用体检-老师试用记录表.xlsx
@@ -658,10 +658,10 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="40" customHeight="1">
+    <row r="7" ht="56.5" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>隐私：普通体检只把参考文献条目发给 Crossref、OpenAlex 等公开数据库；“AI 继续查”、截图识别和论断核查会把相应文字发给 DeepSeek。学生未公开的论文请先征得本人同意。</t>
+          <t>隐私：普通体检把参考文献条目发给 Crossref、OpenAlex 等公开数据库，中文期刊论文还会把题名发给 DeepSeek 的搜索接口（搜索引擎，不是大模型）；“AI 继续查”、截图识别和论断核查会把相应文字发给 DeepSeek 的大模型。学生未公开的论文请先征得本人同意。</t>
         </is>
       </c>
     </row>
